--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104704_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104704_W28.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1195</v>
+        <v>7.5219</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4814</v>
+        <v>4.3741</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6381</v>
+        <v>3.1478</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5155</v>
+        <v>7.494</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1602</v>
+        <v>3.1539</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3553</v>
+        <v>4.3401</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4739</v>
+        <v>7.4207</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4145</v>
+        <v>3.3849</v>
       </c>
       <c r="L2" t="n">
-        <v>4.0594</v>
+        <v>4.0358</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0416</v>
+        <v>0.0732</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9935</v>
+        <v>0.4425</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0948</v>
+        <v>-0.1282</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1013</v>
+        <v>0.5707</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8046</v>
+        <v>2.5908</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4398</v>
+        <v>0.265</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3648</v>
+        <v>2.3258</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1179</v>
+        <v>2.1283</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7127</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4052</v>
+        <v>0.4083</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3441</v>
+        <v>1.3383</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3011</v>
+        <v>1.0755</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2299</v>
+        <v>0.0648</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0712</v>
+        <v>1.0107</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3007</v>
+        <v>2.1265</v>
       </c>
       <c r="E4" t="n">
-        <v>3.415</v>
+        <v>3.1222</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1143</v>
+        <v>-0.9957</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6654</v>
+        <v>0.676</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3188</v>
+        <v>0.3242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3466</v>
+        <v>0.3518</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3061</v>
+        <v>3.2967</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6407</v>
+        <v>-2.6207</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0475</v>
+        <v>-0.1429</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1089</v>
+        <v>-0.1745</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9699</v>
+        <v>1.9128</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4111</v>
+        <v>4.2868</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4412</v>
+        <v>-2.374</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7321</v>
+        <v>1.7329</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4762</v>
+        <v>1.4735</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0292</v>
+        <v>3.006</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9497</v>
+        <v>1.9338</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2971</v>
+        <v>-1.2731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2574</v>
+        <v>-0.324</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2571</v>
+        <v>-0.3534</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0003</v>
+        <v>0.0294</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5678</v>
+        <v>1.5071</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8104</v>
+        <v>1.2503</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3781</v>
+        <v>0.2569</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9519</v>
+        <v>-1.9219</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1385</v>
+        <v>-0.4337</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1866</v>
+        <v>-1.4882</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3672</v>
+        <v>-0.5498</v>
       </c>
       <c r="K6" t="n">
-        <v>1.967</v>
+        <v>-0.7207</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5998</v>
+        <v>0.1708</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5847</v>
+        <v>-1.372</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1715</v>
+        <v>0.287</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>-1.659</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2037</v>
+        <v>-0.5435</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>-0.4879</v>
       </c>
       <c r="U6" t="n">
-        <v>1.113</v>
+        <v>-0.0556</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.2001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.4262</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2001</v>
+        <v>1.398</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2122</v>
+        <v>-1.0033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0121</v>
+        <v>2.4013</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9217</v>
+        <v>1.9507</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4343</v>
+        <v>2.1369</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4874</v>
+        <v>-0.1862</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5359</v>
+        <v>1.3476</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7171</v>
+        <v>1.951</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1812</v>
+        <v>-0.6035</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3858</v>
+        <v>0.6032</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2828</v>
+        <v>0.1859</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6685</v>
+        <v>0.4173</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8614000000000001</v>
+        <v>1.0407</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5565</v>
+        <v>-0.0746</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3049</v>
+        <v>1.1152</v>
       </c>
       <c r="V7" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4387</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4124</v>
+        <v>0.5044</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0338</v>
+        <v>-0.5697</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6214</v>
+        <v>1.074</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1501</v>
+        <v>0.3291</v>
       </c>
       <c r="H8" t="n">
-        <v>0.857</v>
+        <v>-1.692</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0071</v>
+        <v>2.0211</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2788</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4329</v>
+        <v>-1.3175</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7117</v>
+        <v>2.0327</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8712</v>
+        <v>-0.3861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4241</v>
+        <v>-0.3745</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2954</v>
+        <v>-0.0116</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2015</v>
+        <v>0.8095</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3126</v>
+        <v>-0.1467</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8889</v>
+        <v>0.9562</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3216</v>
+        <v>-0.3526</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9407</v>
+        <v>-0.8266</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6191</v>
+        <v>0.474</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1578</v>
+        <v>-1.1529</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6061</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6625</v>
+        <v>-0.6662</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1558</v>
+        <v>0.1173</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U9" t="n">
-        <v>0.434</v>
+        <v>0.2777</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4914</v>
+        <v>-0.5586</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4333</v>
+        <v>0.3241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9419</v>
+        <v>-0.8827</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3299</v>
+        <v>-1.1404</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6985</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0284</v>
+        <v>-2.0018</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7443</v>
+        <v>-0.2842</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3028</v>
+        <v>0.4309</v>
       </c>
       <c r="L10" t="n">
-        <v>2.047</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4143</v>
+        <v>-0.8562</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3957</v>
+        <v>0.4305</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0186</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1824</v>
+        <v>1.216</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0434</v>
+        <v>0.6083</v>
       </c>
       <c r="U10" t="n">
-        <v>0.861</v>
+        <v>0.6077</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5672</v>
+        <v>-4.3647</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3093</v>
+        <v>-4.2191</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2579</v>
+        <v>-0.1456</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3516</v>
+        <v>-4.3612</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8699</v>
+        <v>-1.8779</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4816</v>
+        <v>-2.4833</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.9367</v>
+        <v>-2.9574</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4759</v>
+        <v>-1.4898</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4149</v>
+        <v>-1.4037</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0112</v>
+        <v>0.2241</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3992</v>
+        <v>-0.2812</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4104</v>
+        <v>0.5053</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1459</v>
+        <v>-5.7393</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1328</v>
+        <v>-4.2329</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0132</v>
+        <v>-1.5063</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4271</v>
+        <v>-3.4316</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6707</v>
+        <v>-1.6878</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7565</v>
+        <v>-1.7438</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6801</v>
+        <v>-0.7111</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8667</v>
+        <v>-0.8973</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.747</v>
+        <v>-2.7205</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7764</v>
+        <v>0.1963</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1693</v>
+        <v>-0.2164</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9457</v>
+        <v>0.4127</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8489</v>
+        <v>6.546300000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>2.366799999999998</v>
+        <v>2.770900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4819</v>
+        <v>3.775500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3044</v>
+        <v>2.302999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.383899999999999</v>
+        <v>3.375199999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.079499999999999</v>
+        <v>-1.0723</v>
       </c>
       <c r="J13" t="n">
-        <v>12.1708</v>
+        <v>11.9558</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8145</v>
+        <v>4.674700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>7.356300000000002</v>
+        <v>7.280700000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.866399999999999</v>
+        <v>-9.6525</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4305</v>
+        <v>-1.2996</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.4359</v>
+        <v>-8.3531</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8785</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6099</v>
+        <v>13.6578</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4025</v>
+        <v>4.111499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0564</v>
+        <v>-1.3502</v>
       </c>
       <c r="U13" t="n">
-        <v>5.4589</v>
+        <v>5.4616</v>
       </c>
       <c r="V13" t="n">
-        <v>2.410200000000001</v>
+        <v>2.408</v>
       </c>
       <c r="W13" t="n">
-        <v>8.130800000000001</v>
+        <v>8.099600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.7207</v>
+        <v>-5.6916</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0943</v>
+        <v>2.3525</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7057</v>
+        <v>1.5693</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3886</v>
+        <v>0.7832</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2598</v>
+        <v>0.2586</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1025</v>
+        <v>0.1006</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8187</v>
+        <v>0.803</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8587</v>
+        <v>0.8479</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1654</v>
+        <v>0.094</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1866</v>
+        <v>0.1895</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.865</v>
+        <v>1.624</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7785</v>
+        <v>1.1898</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.4341</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7032</v>
+        <v>2.6725</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6494</v>
+        <v>-1.6459</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3525</v>
+        <v>4.3184</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3866</v>
+        <v>4.3352</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>5.0588</v>
+        <v>5.0182</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6834</v>
+        <v>-1.6628</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0631</v>
+        <v>-0.2777</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.113</v>
+        <v>-0.6415</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0499</v>
+        <v>0.3637</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4821</v>
+        <v>0.4948</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1569</v>
+        <v>1.3492</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6748</v>
+        <v>-0.8544</v>
       </c>
       <c r="G16" t="n">
-        <v>1.512</v>
+        <v>1.5192</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2236</v>
+        <v>2.2203</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7116</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1872</v>
+        <v>3.1659</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0753</v>
+        <v>3.0542</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6752</v>
+        <v>-1.6467</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6028</v>
+        <v>-0.5887</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3711</v>
+        <v>0.1503</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2944</v>
+        <v>-0.3245</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1374</v>
+        <v>0.593</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4318</v>
+        <v>-0.9175</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1273</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4948</v>
+        <v>0.3238</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4238</v>
+        <v>-0.1965</v>
       </c>
       <c r="J17" t="n">
-        <v>0.83</v>
+        <v>1.4017</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6061</v>
+        <v>0.9997</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2239</v>
+        <v>0.4019</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.759</v>
+        <v>-1.2744</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1113</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5984</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3416</v>
+        <v>-0.7281</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6684</v>
+        <v>-0.8087</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6732</v>
+        <v>0.0805</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3634</v>
+        <v>-0.4052</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3687</v>
+        <v>-0.484</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7322</v>
+        <v>0.0789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1101</v>
+        <v>-0.9486</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31</v>
+        <v>-0.6121</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1999</v>
+        <v>-0.3364</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4121</v>
+        <v>0.2247</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0044</v>
+        <v>-0.669</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4078</v>
+        <v>0.8937</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.302</v>
+        <v>-1.1733</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6944</v>
+        <v>0.0568</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6077</v>
+        <v>-1.2301</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7419</v>
+        <v>0.0395</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0434</v>
+        <v>-0.4811</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3015</v>
+        <v>0.5206</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4653</v>
+        <v>-0.4616</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2412</v>
+        <v>1.1809</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2241</v>
+        <v>-1.6425</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3324</v>
+        <v>1.139</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2525</v>
+        <v>-0.9732</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0799</v>
+        <v>2.1122</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6798</v>
+        <v>2.8583</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7171</v>
+        <v>0.1477</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>2.7106</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6526</v>
+        <v>-1.7193</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5354</v>
+        <v>-1.1209</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1172</v>
+        <v>-0.5984</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1866</v>
+        <v>-0.5794</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4386</v>
+        <v>-0.697</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2519</v>
+        <v>0.1176</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.4764</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4843</v>
+        <v>-0.6479</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2215</v>
+        <v>-1.0042</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7058</v>
+        <v>0.3563</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1485</v>
+        <v>-2.6305</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-1.6058</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1138</v>
+        <v>-1.0247</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8906</v>
+        <v>-1.3269</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1692</v>
+        <v>-1.4759</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7214</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.742</v>
+        <v>-1.3036</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1344</v>
+        <v>-0.13</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-1.1736</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6082</v>
+        <v>-0.4727</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.7667</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4783</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8146</v>
+        <v>-0.8368</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9921</v>
+        <v>-0.7161</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1774</v>
+        <v>-0.1207</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6407</v>
+        <v>-1.328</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6119</v>
+        <v>-1.2522</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0289</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3195</v>
+        <v>-0.6835</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4688</v>
+        <v>-0.7207</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1493</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3212</v>
+        <v>-0.6446</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1431</v>
+        <v>-0.5315</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1781</v>
+        <v>-0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6276</v>
+        <v>-0.1917</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.0327</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1376</v>
+        <v>-0.159</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9369</v>
+        <v>-1.1325</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1058</v>
+        <v>-0.4375</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9603</v>
+        <v>0.0823</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6191</v>
+        <v>0.5022</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3411</v>
+        <v>-0.4199</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2305</v>
+        <v>0.8267</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6651</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8956</v>
+        <v>0.2234</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1908</v>
+        <v>-0.7444</v>
       </c>
       <c r="N22" t="n">
-        <v>0.046</v>
+        <v>-0.1011</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2368</v>
+        <v>-0.6433</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4718</v>
+        <v>0.4877</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8347</v>
+        <v>-0.156</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3629</v>
+        <v>0.6437</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1578</v>
+        <v>-2.1398</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2984</v>
+        <v>-2.5507</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1406</v>
+        <v>0.4109</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8676</v>
+        <v>-2.8679</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5326</v>
+        <v>-0.526</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3351</v>
+        <v>-2.342</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0928</v>
+        <v>-2.1091</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2562</v>
+        <v>0.2728</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U23" t="n">
-        <v>0.235</v>
+        <v>0.4868</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7735</v>
+        <v>-3.5826</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.488</v>
+        <v>-4.2075</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7145</v>
+        <v>0.6249</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.308</v>
+        <v>-0.3268</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1158</v>
+        <v>0.0931</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4238</v>
+        <v>-0.4199</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2027</v>
+        <v>0.1567</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3543</v>
+        <v>-0.3942</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5107</v>
+        <v>-0.4835</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9061</v>
+        <v>-0.6805</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1825</v>
+        <v>-0.8296</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2764</v>
+        <v>0.1492</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.848800000000001</v>
+        <v>-5.059600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4821</v>
+        <v>-3.775399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3669</v>
+        <v>-1.2843</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3044</v>
+        <v>-2.3029</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.384</v>
+        <v>-3.375199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.079500000000001</v>
+        <v>1.072199999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>9.866299999999999</v>
+        <v>9.652700000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4308</v>
+        <v>1.299599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>8.435700000000001</v>
+        <v>8.3529</v>
       </c>
       <c r="M25" t="n">
-        <v>-12.1708</v>
+        <v>-11.9558</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.814699999999999</v>
+        <v>-4.674799999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.3563</v>
+        <v>-7.2808</v>
       </c>
       <c r="P25" t="n">
-        <v>2.268200000000001</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.61</v>
+        <v>-13.6578</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4025</v>
+        <v>-2.6248</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.4589</v>
+        <v>-5.4617</v>
       </c>
       <c r="U25" t="n">
-        <v>2.0565</v>
+        <v>2.8369</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.4102</v>
+        <v>-2.408</v>
       </c>
       <c r="W25" t="n">
-        <v>5.7207</v>
+        <v>5.6915</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.1309</v>
+        <v>-8.099600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104704_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104704_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.6916</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104704_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
